--- a/VSL/大賀VSL_スライド構造分析_v1.xlsx
+++ b/VSL/大賀VSL_スライド構造分析_v1.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="【0】 前提と方法論" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="【1】 シーン構造一覧" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="【2】 5デザインパターン" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="【3】 本VSL適用マッピング" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="【4】 結論・運用ルール" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="【5】 シーン順序の根拠" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="【6】 観察ノート" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="【7】 他デッキとの差分" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="【0】 前提と方法論" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="【1】 シーン構造一覧" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="【2】 5デザインパターン" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="【3】 本VSL適用マッピング" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="【4】 結論・運用ルール" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="【5】 シーン順序の根拠" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="【6】 観察ノート" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="【7】 他デッキとの差分" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="【8】 大賀の実績者配置" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="【9】 UTAGE実績者選定" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="【10】 不採用候補・将来活用" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="22">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -155,8 +158,62 @@
       <color rgb="00AAAAAA"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="メイリオ"/>
+      <b val="1"/>
+      <color rgb="00A05000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
+      <b val="1"/>
+      <color rgb="005A7B95"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
+      <b val="1"/>
+      <color rgb="005A7B95"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
+      <b val="1"/>
+      <color rgb="008B6F5A"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
+      <b val="1"/>
+      <color rgb="008B6F5A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
+      <b val="1"/>
+      <color rgb="008B6F5A"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
+      <b val="1"/>
+      <color rgb="008F7B5A"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
+      <b val="1"/>
+      <color rgb="008F7B5A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
+      <b val="1"/>
+      <color rgb="008F7B5A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -253,8 +310,38 @@
         <bgColor rgb="006B8A7A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B0"/>
+        <bgColor rgb="00FFE0B0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005A7B95"/>
+        <bgColor rgb="005A7B95"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0E8F8"/>
+        <bgColor rgb="00E0E8F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B6F5A"/>
+        <bgColor rgb="008B6F5A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008F7B5A"/>
+        <bgColor rgb="008F7B5A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -276,11 +363,55 @@
         <color rgb="00D0D0CC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color rgb="00D0D0CC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color rgb="00D0D0CC"/>
+      </right>
+      <top style="hair">
+        <color rgb="00D0D0CC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color rgb="00D0D0CC"/>
+      </right>
+      <top style="hair">
+        <color rgb="00D0D0CC"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00D0D0CC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color rgb="00D0D0CC"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00D0D0CC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -371,6 +502,41 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -448,7 +614,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>9</col>
@@ -463,14 +629,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -491,14 +657,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -519,14 +685,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -547,14 +713,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -575,14 +741,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -603,14 +769,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -631,14 +797,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -659,14 +825,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -687,14 +853,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -715,14 +881,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -743,14 +909,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId11"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -771,14 +937,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId12"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -799,14 +965,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId13"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -827,14 +993,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -855,14 +1021,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -883,14 +1049,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId16"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -911,14 +1077,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId17"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -939,14 +1105,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId18"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -967,14 +1133,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId19"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -995,14 +1161,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId20"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1023,14 +1189,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId21"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1051,14 +1217,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId22"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1079,14 +1245,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId23"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1107,14 +1273,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId24"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1135,14 +1301,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId25"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1163,14 +1329,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId26"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1191,14 +1357,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId27"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1219,14 +1385,42 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId28"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1343025"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1667,13 +1861,1957 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="49" t="inlineStr">
+        <is>
+          <t>UTAGE VSL 実績者選定 — 新6名のキャスティング根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>お客様の声（写真確認済み30名）から、大賀の『1人=1軸』原則に従って単一軸の最大変化量で6名を選定。配置とのマッチング根拠も併記。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="50" t="inlineStr">
+        <is>
+          <t>A. 新6名の選定理由</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="51" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="51" t="inlineStr">
+        <is>
+          <t>名前</t>
+        </is>
+      </c>
+      <c r="C5" s="51" t="inlineStr">
+        <is>
+          <t>業種</t>
+        </is>
+      </c>
+      <c r="D5" s="51" t="inlineStr">
+        <is>
+          <t>単一軸（最大変化量）</t>
+        </is>
+      </c>
+      <c r="E5" s="51" t="inlineStr">
+        <is>
+          <t>キー数字</t>
+        </is>
+      </c>
+      <c r="F5" s="51" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="G5" s="51" t="inlineStr">
+        <is>
+          <t>選定理由</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="130" customHeight="1">
+      <c r="A7" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>加藤 朋子 様</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>活用事例集2024年版より</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>手作業ゼロ・週次タスク自動化</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>週6時間の手作業 → ほぼゼロ
+月10万円 → 月2万円（80%削減）
+毎月ローンチ可能に</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>新29-2,3
+＋191感情モーメント</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>『週6時間の手作業がゼロ』は雑務ゼロ宣言と最も直接的に紐づく。VSL冒頭の独自概念（雑務ゼロ）を体現する最強の証拠。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="130" customHeight="1">
+      <c r="A8" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>手塚 正人 様</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>マーケティングオートメーション設計・実装／UTAGE構築者育成</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>本業集中・実働1時間化</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>1日数時間 → ゼロ
+実働は個別相談の1時間のみ
+オートウェビナーで集客自動化</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>新29-4,5</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>『実働は個別相談1時間のみ』は本業集中の到達点を象徴。雑務ゼロ後の理想状態を最も簡潔に表現。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="130" customHeight="1">
+      <c r="A9" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>アポロン陽子 様</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Apollo Academy 代表／オンラインビジネスコンサルタント</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>作業時間の劇的圧縮</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>30日分のステップ配信 10日 → 数時間
+メール1本 90分 → 3分
+（圧縮率 数十倍）</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>新29-6,7（スロット枠）</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>圧縮率が最も劇的（10日→数時間／90分→3分）。具体的な体感差が伝わりやすく『日々の雑務が劇的に減った』軸の最強例。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="130" customHeight="1">
+      <c r="A10" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>徳武 輝彦 様</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>ウェビナーづくりの専門家</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>事業ステージ変化（雑務ゼロ → 出版実現）</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>データまとめ 3日 → 0分
+客単価 30万 → 330万円
+売上 1億円突破
+商業出版『UTAGE実践マニュアル』</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>122-2〜122-6 深掘り</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>仕組み完成後の最大変化を体現。『データまとめ0分化』→『売上1億』→『出版』のストーリーは『事業のステージそのものが変わった瞬間』として深掘りに最適。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="130" customHeight="1">
+      <c r="A11" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>大賀 聖也 様</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>ビジネスコミュニティ運営</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>他ツール集約（中途半端反証）</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>ClickFunnels等 10個以上の海外ツール → UTAGE 1個
+月20万円 → 月2万円台（1/10）
+年商 1,500万 → 1億5,000万</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>82-2〜82-5 反論②</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>10個以上の海外ツールを使い倒した経験者がUTAGE 1個に集約した事実は、『中途半端じゃ困る経験者の選択』として最強の反証。「経験者が選んだ」が決定打。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="130" customHeight="1">
+      <c r="A12" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>こんの りり 様</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>オンラインアカデミー運営</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>短期間スピード・運用シンプル化</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>3日で集客スタート
+Web専門家への依頼不要
+スタッフのみで運用可能に
+月17万円の経費削減</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>164-2〜164-4 反論③</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>『3日で集客スタート』は14日トライアル反証として直結。『スタッフのみで運用可能』は『未経験でも14日で動ける』への補強。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="50" t="inlineStr">
+        <is>
+          <t>B. 配置マッピング（どこに誰が登場するか）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="51" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="B16" s="51" t="inlineStr">
+        <is>
+          <t>スライド</t>
+        </is>
+      </c>
+      <c r="C16" s="51" t="inlineStr">
+        <is>
+          <t>テーマ／心理的役割</t>
+        </is>
+      </c>
+      <c r="D16" s="51" t="inlineStr">
+        <is>
+          <t>登場人物</t>
+        </is>
+      </c>
+      <c r="E16" s="51" t="inlineStr">
+        <is>
+          <t>前後文章の流れとの整合性</t>
+        </is>
+      </c>
+      <c r="F16" s="53" t="n"/>
+      <c r="G16" s="47" t="n"/>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>早期実績バッチ①</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>新29-2,3</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>雑務ゼロ宣言直後の最初の証拠</t>
+        </is>
+      </c>
+      <c r="D17" s="54" t="inlineStr">
+        <is>
+          <t>加藤さん</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>直前『毎日の発信を少し減らしても売上が落ちない』直後『3名に共通しているのは雑務ゼロ』→ 加藤さんの『週6時間→ゼロ』が宣言と完全直結</t>
+        </is>
+      </c>
+      <c r="F17" s="53" t="n"/>
+      <c r="G17" s="47" t="n"/>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>早期実績バッチ②</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>新29-4,5</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>本業集中・自動化の到達点</t>
+        </is>
+      </c>
+      <c r="D18" s="54" t="inlineStr">
+        <is>
+          <t>手塚さん</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>前後の宣言（雑務ゼロ）→ 手塚さんの『実働1時間のみ』が到達点として補強</t>
+        </is>
+      </c>
+      <c r="F18" s="53" t="n"/>
+      <c r="G18" s="47" t="n"/>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>早期実績バッチ③（スロット）</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>新29-6,7</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>日々の雑務劇的減少</t>
+        </is>
+      </c>
+      <c r="D19" s="54" t="inlineStr">
+        <is>
+          <t>アポロンさん</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>前後の宣言（雑務ゼロ）→ アポロンさんの『90分→3分』が体感差として響く</t>
+        </is>
+      </c>
+      <c r="F19" s="53" t="n"/>
+      <c r="G19" s="47" t="n"/>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>深掘り（売れる流れ直前）</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>122-2〜122-6</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>事業ステージそのものが変わる物語</t>
+        </is>
+      </c>
+      <c r="D20" s="54" t="inlineStr">
+        <is>
+          <t>徳武さん</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>直前『売れる流れの正体』→ 徳武さんの『データ0分化→売上1億→出版』が物語の頂点を提示</t>
+        </is>
+      </c>
+      <c r="F20" s="53" t="n"/>
+      <c r="G20" s="47" t="n"/>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>反論② 中途半端</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>82-2〜82-5</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>オールインワンの完成度の証拠</t>
+        </is>
+      </c>
+      <c r="D21" s="54" t="inlineStr">
+        <is>
+          <t>大賀さん</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>直前『オールインワンって中途半端では？』→ 大賀さんの『10個の海外ツール経験者がUTAGE 1個』が反証</t>
+        </is>
+      </c>
+      <c r="F21" s="53" t="n"/>
+      <c r="G21" s="47" t="n"/>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>反論③ 14日</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>164-2〜164-4</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>短期間で形にできる証拠</t>
+        </is>
+      </c>
+      <c r="D22" s="54" t="inlineStr">
+        <is>
+          <t>こんのさん</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>直前『14日間でファネル構築できる』→ こんのさんの『3日で集客スタート』が反証</t>
+        </is>
+      </c>
+      <c r="F22" s="53" t="n"/>
+      <c r="G22" s="47" t="n"/>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>感情モーメント</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>191-2,3</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>動かないリスクへの最後の押し</t>
+        </is>
+      </c>
+      <c r="D23" s="54" t="inlineStr">
+        <is>
+          <t>加藤さん（再）</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>直前『動かない選択は静かに悪化』→ 加藤さんの『取り戻した時間』が動く動機を作る</t>
+        </is>
+      </c>
+      <c r="F23" s="53" t="n"/>
+      <c r="G23" s="47" t="n"/>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>6名フル紹介</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>124-140</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>証言6名を1人ずつ深掘り</t>
+        </is>
+      </c>
+      <c r="D24" s="54" t="inlineStr">
+        <is>
+          <t>6名全員</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>クライマックスの社会的証明。各人2-3スライドで業種・ビフォー・アフター・クオート</t>
+        </is>
+      </c>
+      <c r="F24" s="53" t="n"/>
+      <c r="G24" s="47" t="n"/>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>点呼</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>185-2〜185-5</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>あなたも同じ場所にいた感</t>
+        </is>
+      </c>
+      <c r="D25" s="54" t="inlineStr">
+        <is>
+          <t>6名全員（再）</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>クロージング直前『6名全員、ほんの少し前まで同じ場所にいた』で感情のクロージング</t>
+        </is>
+      </c>
+      <c r="F25" s="53" t="n"/>
+      <c r="G25" s="47" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="50" t="inlineStr">
+        <is>
+          <t>C. 写真・許諾ステータス</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="51" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B29" s="51" t="inlineStr">
+        <is>
+          <t>名前</t>
+        </is>
+      </c>
+      <c r="C29" s="51" t="inlineStr">
+        <is>
+          <t>写真</t>
+        </is>
+      </c>
+      <c r="D29" s="51" t="inlineStr">
+        <is>
+          <t>許諾</t>
+        </is>
+      </c>
+      <c r="E29" s="51" t="inlineStr">
+        <is>
+          <t>出典</t>
+        </is>
+      </c>
+      <c r="F29" s="51" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="G29" s="47" t="n"/>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>加藤 朋子 様</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>◯ 公開写真あり</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>◯[確認済み]</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>デザイナーさん共有用お客様の声全量.docx</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>★今回新規採用。本VSL構成にぴったり</t>
+        </is>
+      </c>
+      <c r="G30" s="47" t="n"/>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>手塚 正人 様</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>◯ 公開写真あり</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>◯[確認済み]</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>デザイナーさん共有用お客様の声全量.docx／事例集2026</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr"/>
+      <c r="G31" s="47" t="n"/>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>アポロン陽子 様</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>◯ 公開写真あり</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>◯[確認済み]</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>デザイナーさん共有用お客様の声全量.docx／事例集2026</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr"/>
+      <c r="G32" s="47" t="n"/>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>徳武 輝彦 様</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>◯ 公開写真あり</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>◯[確認済み・★ハイライト]</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>デザイナーさん共有用お客様の声全量.docx／事例集2026</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>前回も採用済</t>
+        </is>
+      </c>
+      <c r="G33" s="47" t="n"/>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>大賀 聖也 様</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>◯ 公開写真あり</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>◯[確認済み・★ハイライト]</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>デザイナーさん共有用お客様の声全量.docx</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>前回も採用済</t>
+        </is>
+      </c>
+      <c r="G34" s="47" t="n"/>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>こんの りり 様</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>◯ 公開写真あり</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>◯[確認済み・★ハイライト]</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>デザイナーさん共有用お客様の声全量.docx／事例集2026</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>前回も採用済</t>
+        </is>
+      </c>
+      <c r="G35" s="47" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="50" t="inlineStr">
+        <is>
+          <t>D. 大賀との配置思想の対比</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="110" customHeight="1">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>大賀は『1ブロック3名×2ブロック＋法人ロゴ』の3段構成。本VSLは独自概念（雑務ゼロ）を主軸にするため、大賀よりも早く実績を投入する必要があり『早期実績バッチ3名（新29）』を雑務ゼロ宣言の直後に追加した。ただし大賀の『1人=1軸／3名で打ち止め／ブロック後に共通点まとめ』のルールは完全踏襲。新6名は全員『単一軸』で勝負しており、複合数字の人物（鈴木 隆寛さんなど）はあえて外した。また大賀がしている『法人ロゴでの権威付け（S025）』は、本VSLでは『1.5万社・100万人の利用実績（S78-80）』で代替。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="E20:G20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="55" t="inlineStr">
+        <is>
+          <t>不採用候補と将来活用考察 — 1枚集合スライド用のストック</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>単一軸として強い実績だが、今回の6名選定からは漏れた候補。
+将来的に『1枚集合スライド（〇〇な方々がこんなに）』として活用する想定で、軸別にグルーピングしてストック。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="56" t="inlineStr">
+        <is>
+          <t>A. 将来活用パターン（1枚集合スライド案）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="57" t="inlineStr">
+        <is>
+          <t>パターン</t>
+        </is>
+      </c>
+      <c r="B5" s="57" t="inlineStr">
+        <is>
+          <t>活用シーン</t>
+        </is>
+      </c>
+      <c r="C5" s="57" t="inlineStr">
+        <is>
+          <t>想定人数</t>
+        </is>
+      </c>
+      <c r="D5" s="57" t="inlineStr">
+        <is>
+          <t>テーマ</t>
+        </is>
+      </c>
+      <c r="E5" s="57" t="inlineStr">
+        <is>
+          <t>効果</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="50" customHeight="1">
+      <c r="A6" s="40" t="inlineStr">
+        <is>
+          <t>A. コスト削減者集合</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>反論②（中途半端／コスト疑問）の補強</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>4-6名</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>他ツール集約・コスト削減</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>『大賀さんだけじゃなく、こんなにいる』の量的証拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="50" customHeight="1">
+      <c r="A7" s="40" t="inlineStr">
+        <is>
+          <t>B. 売上倍増者集合</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>反論『本当に売れる？』への補強</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>4-6名</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>事業ステージ変化・売上3-10倍</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>『徳武さんだけじゃなく』の量的証拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="50" customHeight="1">
+      <c r="A8" s="40" t="inlineStr">
+        <is>
+          <t>C. 雑務削減者集合</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>雑務ゼロ宣言の補強（新29付近）</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>4-6名</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>手作業ゼロ・自動化</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>『加藤・手塚・アポロンさんだけじゃなく』の量的証拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="50" customHeight="1">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>D. スピード達成者集合</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>反論③（14日）の補強</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>3-5名</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>短期間で0→1突破</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>『こんのさんだけじゃなく』の量的証拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1">
+      <c r="A10" s="40" t="inlineStr">
+        <is>
+          <t>E. 全員ロゴ/写真コラージュ</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>S025的に冒頭の権威付けに使用</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>10-15名</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>業種ジャンル網羅</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>『他にもこんなに』の総量による権威付け</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="56" t="inlineStr">
+        <is>
+          <t>B. 不採用候補一覧（軸別グルーピング）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="57" t="inlineStr">
+        <is>
+          <t>軸グループ</t>
+        </is>
+      </c>
+      <c r="B14" s="57" t="inlineStr">
+        <is>
+          <t>名前</t>
+        </is>
+      </c>
+      <c r="C14" s="57" t="inlineStr">
+        <is>
+          <t>業種</t>
+        </is>
+      </c>
+      <c r="D14" s="57" t="inlineStr">
+        <is>
+          <t>キー数字</t>
+        </is>
+      </c>
+      <c r="E14" s="57" t="inlineStr">
+        <is>
+          <t>不採用理由</t>
+        </is>
+      </c>
+      <c r="F14" s="57" t="inlineStr">
+        <is>
+          <t>将来活用先</t>
+        </is>
+      </c>
+      <c r="G14" s="47" t="n"/>
+    </row>
+    <row r="15" ht="38" customHeight="1">
+      <c r="A15" s="58" t="inlineStr">
+        <is>
+          <t>【コスト削減軸】</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>鉾立 由紀 様 ★</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>コンテンツビジネス</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>月15万円 → 月2万円台</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>大賀さんとコスト軸が重複</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>パターンA</t>
+        </is>
+      </c>
+      <c r="G15" s="47" t="n"/>
+    </row>
+    <row r="16" ht="38" customHeight="1">
+      <c r="A16" s="9" t="inlineStr"/>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>中川 瞬 様</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>マーケ・システム会社経営</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>年300万 → 年60万（80%削減）／ROAS 0→300%</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>大賀さんと重複</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>パターンA</t>
+        </is>
+      </c>
+      <c r="G16" s="47" t="n"/>
+    </row>
+    <row r="17" ht="38" customHeight="1">
+      <c r="A17" s="9" t="inlineStr"/>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>高島 吉成 様</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>プロモーションサポート</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>年100万 → 年25万／5つの英語ツール→1つ</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>大賀さんと重複</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>パターンA</t>
+        </is>
+      </c>
+      <c r="G17" s="47" t="n"/>
+    </row>
+    <row r="18" ht="38" customHeight="1">
+      <c r="A18" s="9" t="inlineStr"/>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>小宇佐 拓宏 様</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>オートウェビナー構築支援</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>月15万円→不要／2週間→2-3日</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>大賀さんと重複（集約＋スピード）</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>パターンA／D</t>
+        </is>
+      </c>
+      <c r="G18" s="47" t="n"/>
+    </row>
+    <row r="19" ht="38" customHeight="1">
+      <c r="A19" s="9" t="inlineStr"/>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>ヒロル 様</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>年60万円コスト削減</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>大賀さんと重複</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>パターンA</t>
+        </is>
+      </c>
+      <c r="G19" s="47" t="n"/>
+    </row>
+    <row r="20" ht="38" customHeight="1">
+      <c r="A20" s="9" t="inlineStr"/>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>前田 由紀子 様</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>ツールコスト1/4／業務効率2倍</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>大賀さんと重複</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>パターンA</t>
+        </is>
+      </c>
+      <c r="G20" s="47" t="n"/>
+    </row>
+    <row r="21" ht="38" customHeight="1">
+      <c r="A21" s="9" t="inlineStr"/>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>佐治 邦彦 様</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>外注費月10万円削減／LP制作時間1/4</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>コスト＋自動化複合</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>パターンA</t>
+        </is>
+      </c>
+      <c r="G21" s="47" t="n"/>
+    </row>
+    <row r="22" ht="38" customHeight="1">
+      <c r="A22" s="58" t="inlineStr">
+        <is>
+          <t>【売上倍増軸】</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>渡辺 みゆ 様</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>自動化コンサルタント</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>年商4000万 → 1.2億／ROAS 9000%</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>徳武さんと事業ステージ重複</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>パターンB</t>
+        </is>
+      </c>
+      <c r="G22" s="47" t="n"/>
+    </row>
+    <row r="23" ht="38" customHeight="1">
+      <c r="A23" s="9" t="inlineStr"/>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>秦野 真里 様</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>ジャズレッスン講師</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>年収10倍／セミナー月30回→ほぼゼロ</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>趣味業界の特殊事例</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>パターンB</t>
+        </is>
+      </c>
+      <c r="G23" s="47" t="n"/>
+    </row>
+    <row r="24" ht="38" customHeight="1">
+      <c r="A24" s="9" t="inlineStr"/>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>鈴木 隆寛 様</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>ディズニー就活サポート</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>半年で売上1000万円増／平均単価1.7倍</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>事業ステージ重複</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>パターンB</t>
+        </is>
+      </c>
+      <c r="G24" s="47" t="n"/>
+    </row>
+    <row r="25" ht="38" customHeight="1">
+      <c r="A25" s="9" t="inlineStr"/>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>垣花 夏未 様</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>ボディアートスクール運営</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>年商100万 → 月商100-200万（12倍）</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>事業ステージ重複</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>パターンB</t>
+        </is>
+      </c>
+      <c r="G25" s="47" t="n"/>
+    </row>
+    <row r="26" ht="38" customHeight="1">
+      <c r="A26" s="9" t="inlineStr"/>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>高見 英作 様</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>プロデューサー</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>月商 → 1,000万円以上</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>事業ステージ重複</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>パターンB</t>
+        </is>
+      </c>
+      <c r="G26" s="47" t="n"/>
+    </row>
+    <row r="27" ht="38" customHeight="1">
+      <c r="A27" s="9" t="inlineStr"/>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>中川 瞬 様（再）</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>100万円赤字 → 4,415万円／ROAS 0→300%</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>事業ステージは徳武さんが採用</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>パターンB</t>
+        </is>
+      </c>
+      <c r="G27" s="47" t="n"/>
+    </row>
+    <row r="28" ht="38" customHeight="1">
+      <c r="A28" s="58" t="inlineStr">
+        <is>
+          <t>【雑務削減軸】</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>ジェフ 様</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>幼児教育コンテンツ販売</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>ローンチ時の個別対応2週間 → 0</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>手作業軸は加藤さんが採用</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>パターンC</t>
+        </is>
+      </c>
+      <c r="G28" s="47" t="n"/>
+    </row>
+    <row r="29" ht="38" customHeight="1">
+      <c r="A29" s="9" t="inlineStr"/>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>西山 美穂 様</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>速読講座主宰</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>作業時間4時間削減／個別相談成約率90%</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>手作業軸は加藤さんが採用</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>パターンC</t>
+        </is>
+      </c>
+      <c r="G29" s="47" t="n"/>
+    </row>
+    <row r="30" ht="38" customHeight="1">
+      <c r="A30" s="9" t="inlineStr"/>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>りんちゃん 様</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>ママ起業家プロデューサー</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>手動対応70%削減／予約率3倍</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>手作業軸は加藤さんが採用</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>パターンC</t>
+        </is>
+      </c>
+      <c r="G30" s="47" t="n"/>
+    </row>
+    <row r="31" ht="38" customHeight="1">
+      <c r="A31" s="9" t="inlineStr"/>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>灘本 敏 様</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>マーケ支援・ディレクター養成</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>反応率約2倍／1人→チーム化</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>軸が複合的</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>パターンC／E</t>
+        </is>
+      </c>
+      <c r="G31" s="47" t="n"/>
+    </row>
+    <row r="32" ht="38" customHeight="1">
+      <c r="A32" s="9" t="inlineStr"/>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>齋藤 たいき 様</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>AI×クリエイティブ教育</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>受講生サポート 60名→600名（スケール10倍）</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>軸が複合的（スケール）</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>パターンC</t>
+        </is>
+      </c>
+      <c r="G32" s="47" t="n"/>
+    </row>
+    <row r="33" ht="38" customHeight="1">
+      <c r="A33" s="9" t="inlineStr"/>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>おでん 様</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>LINE/UTAGE構築者育成講座</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>工数1/4／売上2倍</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>軸が複合的</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>パターンC</t>
+        </is>
+      </c>
+      <c r="G33" s="47" t="n"/>
+    </row>
+    <row r="34" ht="38" customHeight="1">
+      <c r="A34" s="58" t="inlineStr">
+        <is>
+          <t>【スピード軸】</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>城山 恒予 様</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>UTAGEデザイナー養成講座</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>1ヶ月で売上120万円／リスト0からの0→1</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>こんのさんと重複</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>パターンD</t>
+        </is>
+      </c>
+      <c r="G34" s="47" t="n"/>
+    </row>
+    <row r="35" ht="38" customHeight="1">
+      <c r="A35" s="9" t="inlineStr"/>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>エイゴフル 様</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>英検対策コーチング</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>独立半年、仕組み化から1ヶ月で売上100万円</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>こんのさんと重複</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>パターンD</t>
+        </is>
+      </c>
+      <c r="G35" s="47" t="n"/>
+    </row>
+    <row r="36" ht="38" customHeight="1">
+      <c r="A36" s="9" t="inlineStr"/>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>竹原 芳美 様</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>販売準備2週間 → 3日</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>こんのさんと重複</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>パターンD</t>
+        </is>
+      </c>
+      <c r="G36" s="47" t="n"/>
+    </row>
+    <row r="37" ht="38" customHeight="1">
+      <c r="A37" s="9" t="inlineStr"/>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>いのうえ ゆうこ 様</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>ポイ活講座運営</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>ローンチ準備『7人×2ヶ月』→『1人×1日』</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>こんのさんと重複</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>パターンD</t>
+        </is>
+      </c>
+      <c r="G37" s="47" t="n"/>
+    </row>
+    <row r="38" ht="38" customHeight="1">
+      <c r="A38" s="58" t="inlineStr">
+        <is>
+          <t>【特殊軸】</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>水野 彩香 様</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>オンライン秘書養成講座</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>年間総収益2,500万円／秘書講座成約率86.2%</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>売れた後の自動化（独自テーマ）</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>パターンB／C</t>
+        </is>
+      </c>
+      <c r="G38" s="47" t="n"/>
+    </row>
+    <row r="39" ht="38" customHeight="1">
+      <c r="A39" s="9" t="inlineStr"/>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>矢野 徹 様</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>釣りジャンル</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>成約率約2倍</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>ニッチジャンル特殊</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>パターンB</t>
+        </is>
+      </c>
+      <c r="G39" s="47" t="n"/>
+    </row>
+    <row r="40" ht="38" customHeight="1">
+      <c r="A40" s="9" t="inlineStr"/>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>三澤 勇一 様</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>投資AI活用講座</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>LTV 20万 → 60万（3倍）</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>金融系で特殊</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>パターンB</t>
+        </is>
+      </c>
+      <c r="G40" s="47" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="56" t="inlineStr">
+        <is>
+          <t>C. このリストを使う際のメモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="110" customHeight="1">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>▼ 軸別グルーピングが既にできているので、A/Bテストで『6名フル紹介 vs 6名＋集合スライド1枚』を比較可能。
+▼ パターンE（全員ロゴコラージュ）は、新6名で物足りなさを感じた時の補強カードとして温存しておく。
+▼ 写真許諾の最終確認は配置決定後に各人へ再連絡が必要。許諾OKでも『この数字をVSLで出していい？』は別途確認推奨。
+▼ 各候補者は『デザイナーさん共有用お客様の声全量.docx』に詳細プロフィールあり。集合スライド制作時に再参照する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="33">
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="F14:G14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1699,7 +3837,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>観察した172スライドを28シーンに分割。各シーンの心理的役割（意図仮説）／使用パターン／推定尺／代表スクショ／観察メモを対応表化。</t>
+          <t>観察した172スライドを29シーンに分割。各シーンの心理的役割（意図仮説）／使用パターン／推定尺／代表スクショ／観察メモを対応表化。</t>
         </is>
       </c>
     </row>
@@ -2594,17 +4732,17 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>091-099</t>
+          <t>094-096</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>受講者ビフォーアフター</t>
+          <t>第1ケースブロック（外部証拠）</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>実績者の変化で『自分にもできる』</t>
+          <t>個別ケースカードで『あなたも同じ立場から変われる』感を作る（解決策の証拠）</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
@@ -2614,23 +4752,23 @@
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>顔写真＋業種＋ビフォーアフター数字</t>
+          <t>顔写真＋業種＋数字3-4点＋クオート（1人=1単一軸）</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>150秒</t>
+          <t>80秒</t>
         </is>
       </c>
       <c r="H23" s="9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="K23" s="11" t="inlineStr">
         <is>
-          <t>9名の実績者を連続提示。1名あたり約17秒＝畳み掛け。事例集で挟むのが大賀流</t>
+          <t>【訂正】当初『9名連続』と分類したが実数は3名（佐藤ともかさん・みさっきーさん・渡邊みゆさん）。各1人1テーマで数字3-4点の単一軸を徹底。</t>
         </is>
       </c>
     </row>
@@ -2864,49 +5002,51 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="110" customHeight="1">
-      <c r="A29" s="8" t="n">
-        <v>25</v>
+    <row r="29" ht="130" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>135-140</t>
+          <t>133-136</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>3つのコア再強調＋まとめ</t>
+          <t>第2ケースブロック（内部実証）</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>講座中身を再確認、購入前ブリーフ</t>
+          <t>SFCメンバーで『このプログラムで実際に変わった』内部実証。第1ブロック（外部証拠）→第2（内部実証）の2段構成</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>③白</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>ピラミッド＋まとめ箇条書き</t>
+          <t>顔写真左＋業種小キャプション＋右側に数字3-4点（同型レイアウト反復）</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>100秒</t>
+          <t>80秒</t>
         </is>
       </c>
       <c r="H29" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K29" s="11" t="inlineStr">
         <is>
-          <t>シーン14のピラミッドを再登場（今度はチェック付き）。記憶定着＋達成感</t>
+          <t>SFC内部メンバー3名（宮坂龍馬さん・事務局鈴木さん・ツッチーさん）＋S136『この3名に共通しているのは』で締め。畳み掛けすぎず単一軸を保つ</t>
         </is>
       </c>
     </row>
@@ -2916,43 +5056,43 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>141-160</t>
+          <t>135-140</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>プログラム紹介・体制</t>
+          <t>3つのコア再強調＋まとめ</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>中身＋向き不向き＋チーム体制提示</t>
+          <t>講座中身を再確認、購入前ブリーフ</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>①③④</t>
+          <t>③</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>向き不向き赤強調＋セッション名提示＋SFC体制</t>
+          <t>ピラミッド＋まとめ箇条書き</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>300秒</t>
+          <t>100秒</t>
         </is>
       </c>
       <c r="H30" s="9" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K30" s="11" t="inlineStr">
         <is>
-          <t>最も長いブロック。向き不向き（こんな人には向いていません）でセレクション圧をかける</t>
+          <t>シーン14のピラミッドを再登場（今度はチェック付き）。記憶定着＋達成感</t>
         </is>
       </c>
     </row>
@@ -2962,43 +5102,43 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>162-170</t>
+          <t>141-160</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>3つの道の選択</t>
+          <t>プログラム紹介・体制</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>自己選択感／危機感／パートナーシップ宣言</t>
+          <t>中身＋向き不向き＋チーム体制提示</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>①＋④</t>
+          <t>①③④</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>極大文字3つの道／景色写真／スピード警告</t>
+          <t>向き不向き赤強調＋セッション名提示＋SFC体制</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>180秒</t>
+          <t>300秒</t>
         </is>
       </c>
       <c r="H31" s="9" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K31" s="11" t="inlineStr">
         <is>
-          <t>3つの道（閉じる／独学／一緒に）は古典的だが効く。景色写真で『道』を視覚化する演出が秀逸</t>
+          <t>最も長いブロック。向き不向き（こんな人には向いていません）でセレクション圧をかける</t>
         </is>
       </c>
     </row>
@@ -3008,51 +5148,97 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
+          <t>162-170</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>3つの道の選択</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>自己選択感／危機感／パートナーシップ宣言</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>①＋④</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>極大文字3つの道／景色写真／スピード警告</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>180秒</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="I32" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="K32" s="11" t="inlineStr">
+        <is>
+          <t>3つの道（閉じる／独学／一緒に）は古典的だが効く。景色写真で『道』を視覚化する演出が秀逸</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
           <t>171-172</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>最終CTA・希少性・謝辞</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>希少性で行動促進＋温かく締め</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr">
         <is>
           <t>①グラデ</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F33" s="9" t="inlineStr">
         <is>
           <t>予約枠警告＋ありがとう謝辞</t>
         </is>
       </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr">
         <is>
           <t>30秒</t>
         </is>
       </c>
-      <c r="H32" s="9" t="n">
+      <c r="H33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I32" s="9" t="n">
+      <c r="I33" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="K32" s="11" t="inlineStr">
+      <c r="K33" s="11" t="inlineStr">
         <is>
           <t>枠数限定で煽り、最後は『ありがとう』で温かく締める。煽りと感謝のバランスが大賀流</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="27" t="inlineStr"/>
-    </row>
     <row r="36">
-      <c r="A36" s="28" t="inlineStr">
+      <c r="A36" s="27" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>v1.1 (2026-05-27) / 観察者: 制作チーム / 次回改訂予定: A/Bテスト結果反映後</t>
         </is>
@@ -5077,7 +7263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5565,6 +7751,23 @@
       <c r="A34" s="28" t="inlineStr">
         <is>
           <t>v1.1 (2026-05-27) / 観察者: 制作チーム / 次回改訂予定: A/Bテスト結果反映後</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>【訂正】scene 19/25</t>
+        </is>
+      </c>
+      <c r="B36" s="42" t="inlineStr">
+        <is>
+          <t>✏ 訂正</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>初版（v1.0）で『シーン19=9名連続BA』と書いたが、再カウントしたら実数は3名のみ。さらに後段（S133-136）に同様のケースブロック3名（SFCメンバー）があり、合計6名で2ブロック構成。これは本VSLの『早期実績バッチ3名＋6名フル紹介＋点呼』構造と本質的に同じ配置思想。</t>
         </is>
       </c>
     </row>
@@ -5751,4 +7954,387 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="43" t="inlineStr">
+        <is>
+          <t>大賀VSLの実績者配置戦略 — 3段配置と単一軸主義</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>全172スライドから実績者の出方を抽出した結果。当初『9名連続BA』と分類したが訂正：実際は『6名×2ブロック＋冒頭の権威ロゴ』の3段構成だった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="44" t="inlineStr">
+        <is>
+          <t>A. 大賀の3段配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="45" t="inlineStr">
+        <is>
+          <t>段</t>
+        </is>
+      </c>
+      <c r="B5" s="45" t="inlineStr">
+        <is>
+          <t>タイミング</t>
+        </is>
+      </c>
+      <c r="C5" s="45" t="inlineStr">
+        <is>
+          <t>形式</t>
+        </is>
+      </c>
+      <c r="D5" s="45" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E5" s="45" t="inlineStr">
+        <is>
+          <t>心理的役割</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="110" customHeight="1">
+      <c r="A6" s="40" t="inlineStr">
+        <is>
+          <t>第0段
+冒頭(S025)</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>VSL開始 25秒地点</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>法人クライアントロゴ集</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>SHIFT AI のマーケ統括／ピアノショップ／その他法人ロゴ3-5社（個人事例ではなく企業名）</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>権威の借用 — 『この人は本物』と最初の30秒で確認させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="110" customHeight="1">
+      <c r="A7" s="40" t="inlineStr">
+        <is>
+          <t>第1段
+中盤(S094-096)</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>解決策提示後の中盤</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>個別ケースカード × 3名</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>①佐藤ともかさん：心理技術／500万HC銀振一括→売上1.5億・法人化
+②みさっきーさん：脱・教員/才能発掘／単価220万HC連続成約・月最高1050万
+③渡邊みゆさん：SNS自動集客／月商1680万・年売上1億UP</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>解決策の証拠 — 『同じ立場のあなたも変われる』感を作る</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="110" customHeight="1">
+      <c r="A8" s="40" t="inlineStr">
+        <is>
+          <t>第2段
+後半(S133-136)</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>プログラム紹介前の後半</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>SFC内部メンバー × 3名 ＋ 共通点まとめ</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>①宮坂龍馬さん：採用顧問／月50万顧問契約→広告費40万・月商1600万達成
+②事務局鈴木さん：業務外注化／約11ヶ月で2年目1億2000万売上UP
+③ツッチーさん：日本最大級恋愛スクール／広告代理店失敗→ファネル黒字化
+＋S136『この3名に共通しているのは』で締め</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>プログラムの実証 — 『このプログラムで実際に変わった人』として購入動機を後押し</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="44" t="inlineStr">
+        <is>
+          <t>B. 観察された実装上のルール</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="50" customHeight="1">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>1人 = 1軸の徹底</t>
+        </is>
+      </c>
+      <c r="C12" s="46" t="inlineStr">
+        <is>
+          <t>各人物のケースカードには数字3-4点あるが、すべて同じテーマ（売上系か、自動化系か、スピード系か）に揃えている。混合軸を見せない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>各ブロック3名で打ち止め</t>
+        </is>
+      </c>
+      <c r="C13" s="46" t="inlineStr">
+        <is>
+          <t>1ブロック3名以上に増やさない。畳み掛けすぎると個別の印象が薄れる。3名は『1人なら偶然／2人なら傾向／3人で確信』の心理学的最小数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="50" customHeight="1">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>ブロック間に役割の差</t>
+        </is>
+      </c>
+      <c r="C14" s="46" t="inlineStr">
+        <is>
+          <t>第1ブロック（外部証拠）と第2ブロック（内部実証=SFCメンバー）で機能を分ける。同じ目的の繰り返しではなく『信頼の階段』を作る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="50" customHeight="1">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>各人物に同型レイアウト</t>
+        </is>
+      </c>
+      <c r="C15" s="46" t="inlineStr">
+        <is>
+          <t>顔写真左／業種小キャプション／右側に数字3-4点＋クオート。レイアウトを揃えて『同じ型で誰でも再現可能』という暗示。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="50" customHeight="1">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>冒頭は個人ではなく法人</t>
+        </is>
+      </c>
+      <c r="C16" s="46" t="inlineStr">
+        <is>
+          <t>S025は個人ケースではなく法人ロゴ集。順序：法人で権威→個人で共感、の2段。最初から個人事例だと『その人の特例』に見えるリスクを避ける。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="50" customHeight="1">
+      <c r="A17" s="32" t="inlineStr">
+        <is>
+          <t>ブロック後に必ず締め一言</t>
+        </is>
+      </c>
+      <c r="C17" s="46" t="inlineStr">
+        <is>
+          <t>S136『この3名に共通しているのは〜』のように、3名提示後に1スライドで『共通点』を抽出。視聴者が散漫にならず本筋へ戻す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="44" t="inlineStr">
+        <is>
+          <t>C. 本VSLでの採用と独自要素</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="45" t="inlineStr">
+        <is>
+          <t>大賀の配置</t>
+        </is>
+      </c>
+      <c r="B21" s="45" t="inlineStr">
+        <is>
+          <t>本VSLでの対応</t>
+        </is>
+      </c>
+      <c r="C21" s="45" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="D21" s="45" t="inlineStr">
+        <is>
+          <t>判断根拠</t>
+        </is>
+      </c>
+      <c r="E21" s="47" t="n"/>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>第0段：法人ロゴ集(S025)</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>本VSL S78-80：1.5万社・100万人の利用実績</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>代替</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>UTAGEはツール商材なので『個別法人名』ではなく『総導入数』で権威を表現。</t>
+        </is>
+      </c>
+      <c r="E22" s="47" t="n"/>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>第1段：個別ケース3名(中盤)</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>本VSL：新29 早期実績バッチ3名＋6名フル紹介(124-140)</t>
+        </is>
+      </c>
+      <c r="C23" s="48" t="inlineStr">
+        <is>
+          <t>拡張採用</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>大賀は中盤1ブロックだが、本VSLは『早期実績バッチ(新29)』を雑務ゼロ宣言の直後に追加。独自の概念名(雑務ゼロ)を据えるための前倒し配置。</t>
+        </is>
+      </c>
+      <c r="E23" s="47" t="n"/>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>第2段：SFC内部実証3名(後半)</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>本VSL：6名フル紹介(124-140)＋クロージング点呼(185-2)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>圧縮統合</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>本VSLは『SFCメンバー』のような内部組織を持たないため、第1ブロックと第2ブロックを統合して6名フル紹介に集約。クロージング前の点呼で再登場させる。</t>
+        </is>
+      </c>
+      <c r="E24" s="47" t="n"/>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>ブロック後の締め(S136)</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>本VSL S138『共通しているのは雑務ゼロ』</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>完全採用</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>『3名（または6名）に共通しているのは』→『たった一つ、〇〇』という締めはそのまま踏襲。</t>
+        </is>
+      </c>
+      <c r="E25" s="47" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="A13:B13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/VSL/大賀VSL_スライド構造分析_v1.xlsx
+++ b/VSL/大賀VSL_スライド構造分析_v1.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -210,6 +210,11 @@
       <b val="1"/>
       <color rgb="008F7B5A"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
+      <color rgb="002D3748"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="22">
@@ -410,7 +415,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -536,6 +541,15 @@
     <xf numFmtId="0" fontId="30" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -613,6 +627,316 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2667000" cy="1504950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2667000" cy="1504950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2667000" cy="1504950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2667000" cy="1504950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2667000" cy="1504950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2667000" cy="1504950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -3417,7 +3741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3427,6 +3751,7 @@
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3486,7 +3811,13 @@
           <t>選定理由</t>
         </is>
       </c>
-    </row>
+      <c r="H5" s="59" t="inlineStr">
+        <is>
+          <t>顔写真</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="130" customHeight="1"/>
     <row r="7" ht="130" customHeight="1">
       <c r="A7" s="52" t="n">
         <v>1</v>
@@ -4281,6 +4612,7 @@
     <mergeCell ref="E20:G20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4290,7 +4622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4638,8 +4970,84 @@
       </c>
       <c r="E25" s="47" t="n"/>
     </row>
+    <row r="28">
+      <c r="A28" s="44" t="inlineStr">
+        <is>
+          <t>D. 実物：個別ケースカード6名（実スクショ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t>第1ブロック（中盤・S094-096）— 外部証拠としての3名</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="170" customHeight="1"/>
+    <row r="31" ht="55" customHeight="1">
+      <c r="A31" s="60" t="inlineStr">
+        <is>
+          <t>S094 佐藤ともかさん
+心理技術と芸術療法
+→ 売上1.5億・法人化</t>
+        </is>
+      </c>
+      <c r="C31" s="60" t="inlineStr">
+        <is>
+          <t>S095 みさっきーさん＋渡邊みゆさん
+（2名同時表示）
+→ 単価220万・月最高1050万 / 月商1680万</t>
+        </is>
+      </c>
+      <c r="E31" s="60" t="inlineStr">
+        <is>
+          <t>S096 渡邊みゆさん拡大
+SNS自動集客
+→ 年売上1億UP</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="32" t="inlineStr">
+        <is>
+          <t>第2ブロック（クロージング直前・S133-135）— SFC内部メンバー3名</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="170" customHeight="1"/>
+    <row r="35" ht="55" customHeight="1">
+      <c r="A35" s="60" t="inlineStr">
+        <is>
+          <t>S133 宮坂龍馬さん
+社会福祉法人向け採用顧問
+→ 月50万顧問→月商1600万</t>
+        </is>
+      </c>
+      <c r="C35" s="60" t="inlineStr">
+        <is>
+          <t>S134 事務局鈴木さん
+業務外注化の中
+→ 約11ヶ月で2年目1億2000万UP</t>
+        </is>
+      </c>
+      <c r="E35" s="60" t="inlineStr">
+        <is>
+          <t>S135 ツッチーさん
+日本最大級恋愛スクール
+→ 広告代理店失敗→ファネル黒字化</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="50" customHeight="1">
+      <c r="A37" s="61" t="inlineStr">
+        <is>
+          <t>各カードの共通レイアウト：顔写真（左or上）／業種小キャプション／右側に数字3-4点／背景は白＋アクセント色帯／同型レイアウトの反復で処理コスト最小化</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="26">
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A11:E11"/>
@@ -4649,21 +5057,26 @@
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="C17:E17"/>
+    <mergeCell ref="A37:E37"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A33:E33"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="D25:E25"/>
+    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="D24:E24"/>
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="A13:B13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
